--- a/월급 합.xlsx
+++ b/월급 합.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\개인정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0FED04-B893-45D7-A3B2-CD18A8B790E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56175C6E-BD0C-4C6C-BC8F-80E27AD1D8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C1528A54-3910-4F15-91EB-4B5E9EB80605}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="11">
   <si>
     <t>날짜</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,6 +68,18 @@
   </si>
   <si>
     <t>세후</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비과세</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세전-비과세</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>합</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -435,15 +447,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C88C475-9096-4A23-B32E-2E5ED6AECE6A}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.125" customWidth="1"/>
+    <col min="5" max="5" width="11.625" customWidth="1"/>
+    <col min="7" max="7" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.125" customWidth="1"/>
+    <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -454,10 +469,16 @@
         <v>7</v>
       </c>
       <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45951</v>
       </c>
@@ -467,17 +488,24 @@
       <c r="C2">
         <v>1378684</v>
       </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E2">
+        <f>B2-D2</f>
+        <v>1394354</v>
+      </c>
+      <c r="F2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" t="s">
         <v>5</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45982</v>
       </c>
@@ -487,22 +515,33 @@
       <c r="C3">
         <v>1973020</v>
       </c>
-      <c r="D3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="D3">
+        <v>200000</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E16" si="0">B3-D3</f>
+        <v>2075000</v>
+      </c>
+      <c r="F3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="1">
         <v>46163</v>
       </c>
-      <c r="G3">
-        <f>SUMIF($D$2:D12,"월급",$B$2:B12)</f>
-        <v>21816935</v>
-      </c>
-      <c r="H3">
-        <f>SUMIF($D$2:D12,"상여",$B$2:B12)</f>
+      <c r="I3">
+        <f>SUMIF($F$2:F12,"월급",$E$2:E12)</f>
+        <v>20416935</v>
+      </c>
+      <c r="J3">
+        <f>SUMIF($F$2:F12,"상여",$B$2:B12)</f>
         <v>600000</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K3">
+        <f>SUM(I3:J3)</f>
+        <v>21016935</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46010</v>
       </c>
@@ -512,44 +551,63 @@
       <c r="C4">
         <v>1973020</v>
       </c>
-      <c r="D4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="D4">
+        <v>200000</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>2075000</v>
+      </c>
+      <c r="F4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="1">
         <v>46194</v>
       </c>
-      <c r="G4">
-        <f>SUMIF($D$2:D13,"월급",$B$2:B13)</f>
-        <v>25066935</v>
-      </c>
-      <c r="H4">
-        <f>SUMIF($D$2:D13,"상여",$B$2:B13)</f>
+      <c r="I4">
+        <f>SUMIF($F$2:F13,"월급",$E$2:E13)</f>
+        <v>23466935</v>
+      </c>
+      <c r="J4">
+        <f>SUMIF($F$2:F13,"상여",$B$2:B13)</f>
         <v>600000</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K4">
+        <f t="shared" ref="K4:K7" si="1">SUM(I4:J4)</f>
+        <v>24066935</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46022</v>
       </c>
       <c r="B5">
         <v>300000</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>300000</v>
+      </c>
+      <c r="F5" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="1">
+      <c r="H5" s="1">
         <v>46224</v>
       </c>
-      <c r="G5">
-        <f>SUMIF($D$2:D14,"월급",$B$2:B14)</f>
-        <v>28316935</v>
-      </c>
-      <c r="H5">
-        <f>SUMIF($D$2:D14,"상여",$B$2:B14)</f>
+      <c r="I5">
+        <f>SUMIF($F$2:F14,"월급",$E$2:E14)</f>
+        <v>26516935</v>
+      </c>
+      <c r="J5">
+        <f>SUMIF($F$2:F14,"상여",$B$2:B14)</f>
         <v>600000</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="K5">
+        <f t="shared" si="1"/>
+        <v>27116935</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46043</v>
       </c>
@@ -559,22 +617,63 @@
       <c r="C6">
         <v>2537001</v>
       </c>
-      <c r="D6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D6">
+        <v>200000</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>2672581</v>
+      </c>
+      <c r="F6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="1">
+        <v>46255</v>
+      </c>
+      <c r="I6">
+        <f>SUMIF($F$2:F15,"월급",$E$2:E15)</f>
+        <v>29566935</v>
+      </c>
+      <c r="J6">
+        <f>SUMIF($F$2:F15,"상여",$B$2:B15)</f>
+        <v>600000</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="1"/>
+        <v>30166935</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46066</v>
       </c>
       <c r="B7">
         <v>200000</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>200000</v>
+      </c>
+      <c r="F7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H7" s="1">
+        <v>46286</v>
+      </c>
+      <c r="I7">
+        <f>SUMIF($F$2:F16,"월급",$E$2:E16)</f>
+        <v>32616935</v>
+      </c>
+      <c r="J7">
+        <f>SUMIF($F$2:F16,"상여",$B$2:B16)</f>
+        <v>600000</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="1"/>
+        <v>33216935</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46073</v>
       </c>
@@ -584,11 +683,18 @@
       <c r="C8">
         <v>2908480</v>
       </c>
-      <c r="D8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D8">
+        <v>200000</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>3050000</v>
+      </c>
+      <c r="F8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46101</v>
       </c>
@@ -598,11 +704,18 @@
       <c r="C9">
         <v>2868100</v>
       </c>
-      <c r="D9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D9">
+        <v>200000</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>3050000</v>
+      </c>
+      <c r="F9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46133</v>
       </c>
@@ -612,51 +725,119 @@
       <c r="C10">
         <v>2915630</v>
       </c>
-      <c r="D10" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D10">
+        <v>200000</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>3050000</v>
+      </c>
+      <c r="F10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46142</v>
       </c>
       <c r="B11">
         <v>100000</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>100000</v>
+      </c>
+      <c r="F11" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46163</v>
       </c>
       <c r="B12">
         <v>3250000</v>
       </c>
-      <c r="D12" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D12">
+        <v>200000</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>3050000</v>
+      </c>
+      <c r="F12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46194</v>
       </c>
       <c r="B13">
         <v>3250000</v>
       </c>
-      <c r="D13" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D13">
+        <v>200000</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>3050000</v>
+      </c>
+      <c r="F13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46224</v>
       </c>
       <c r="B14">
         <v>3250000</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14">
+        <v>200000</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>3050000</v>
+      </c>
+      <c r="F14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B15">
+        <v>3250000</v>
+      </c>
+      <c r="D15">
+        <v>200000</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>3050000</v>
+      </c>
+      <c r="F15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B16">
+        <v>3250000</v>
+      </c>
+      <c r="D16">
+        <v>200000</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>3050000</v>
+      </c>
+      <c r="F16" t="s">
         <v>3</v>
       </c>
     </row>

--- a/월급 합.xlsx
+++ b/월급 합.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\개인정보\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\GitHub\House_buying_manual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56175C6E-BD0C-4C6C-BC8F-80E27AD1D8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0ED33A7-CCA1-4E43-8F9F-70AF003D1963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C1528A54-3910-4F15-91EB-4B5E9EB80605}"/>
   </bookViews>
@@ -758,6 +758,9 @@
       <c r="B12">
         <v>3250000</v>
       </c>
+      <c r="C12">
+        <v>3008330</v>
+      </c>
       <c r="D12">
         <v>200000</v>
       </c>
